--- a/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-phan-cong-GVHD.xlsx
+++ b/backend/InternLink/InternLink.API/Templates/importTemplates/Mau-danh-sach-phan-cong-GVHD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\internlink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\InternLink\backend\InternLink\InternLink.API\Templates\importTemplates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A49760-C324-4C0C-B504-5A97850DD99C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43318F95-9EC0-491F-91DD-105B25937460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,11 +164,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,36 +486,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>11</v>
       </c>
     </row>
